--- a/STEP1_REVISED/Step1_Stratified_Split.xlsx
+++ b/STEP1_REVISED/Step1_Stratified_Split.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,11 @@
           <t>Vch</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RPM_Region</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -476,6 +481,11 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -496,6 +506,11 @@
       <c r="F3" t="n">
         <v>0.023115971</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -516,6 +531,11 @@
       <c r="F4" t="n">
         <v>0.09732608700000001</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -536,6 +556,11 @@
       <c r="F5" t="n">
         <v>0.151308161</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -556,6 +581,11 @@
       <c r="F6" t="n">
         <v>0.182132285</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -576,6 +606,11 @@
       <c r="F7" t="n">
         <v>0.214618498</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -596,6 +631,11 @@
       <c r="F8" t="n">
         <v>0.235425874</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -616,6 +656,11 @@
       <c r="F9" t="n">
         <v>0.255832691</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -636,6 +681,11 @@
       <c r="F10" t="n">
         <v>0.281800324</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -656,6 +706,11 @@
       <c r="F11" t="n">
         <v>0.305679394</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -676,6 +731,11 @@
       <c r="F12" t="n">
         <v>0.316379708</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -696,6 +756,11 @@
       <c r="F13" t="n">
         <v>0.329237345</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -716,6 +781,11 @@
       <c r="F14" t="n">
         <v>0.35335845</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -736,6 +806,11 @@
       <c r="F15" t="n">
         <v>0.367215621</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -756,6 +831,11 @@
       <c r="F16" t="n">
         <v>0</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -776,6 +856,11 @@
       <c r="F17" t="n">
         <v>0.032958996</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -796,6 +881,11 @@
       <c r="F18" t="n">
         <v>0.109532278</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -816,6 +906,11 @@
       <c r="F19" t="n">
         <v>0.154289085</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -836,6 +931,11 @@
       <c r="F20" t="n">
         <v>0.193668002</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -856,6 +956,11 @@
       <c r="F21" t="n">
         <v>0.219689143</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -876,6 +981,11 @@
       <c r="F22" t="n">
         <v>0.249950795</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -896,6 +1006,11 @@
       <c r="F23" t="n">
         <v>0.267641886</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -916,6 +1031,11 @@
       <c r="F24" t="n">
         <v>0.281931145</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -936,6 +1056,11 @@
       <c r="F25" t="n">
         <v>0.298662612</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -956,6 +1081,11 @@
       <c r="F26" t="n">
         <v>0.306444136</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -976,6 +1106,11 @@
       <c r="F27" t="n">
         <v>0.325507275</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -996,6 +1131,11 @@
       <c r="F28" t="n">
         <v>0.330783285</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1016,6 +1156,11 @@
       <c r="F29" t="n">
         <v>0.348468826</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1036,6 +1181,11 @@
       <c r="F30" t="n">
         <v>0</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1056,6 +1206,11 @@
       <c r="F31" t="n">
         <v>0.049264635</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1076,6 +1231,11 @@
       <c r="F32" t="n">
         <v>0.115556899</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1096,6 +1256,11 @@
       <c r="F33" t="n">
         <v>0.166143722</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1116,6 +1281,11 @@
       <c r="F34" t="n">
         <v>0.202004309</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1136,6 +1306,11 @@
       <c r="F35" t="n">
         <v>0.221703929</v>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1156,6 +1331,11 @@
       <c r="F36" t="n">
         <v>0.246525338</v>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1176,6 +1356,11 @@
       <c r="F37" t="n">
         <v>0.260389238</v>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1196,6 +1381,11 @@
       <c r="F38" t="n">
         <v>0.276412389</v>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1216,6 +1406,11 @@
       <c r="F39" t="n">
         <v>0.286991054</v>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1236,6 +1431,11 @@
       <c r="F40" t="n">
         <v>0.299641021</v>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1256,6 +1456,11 @@
       <c r="F41" t="n">
         <v>0.303544856</v>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1276,6 +1481,11 @@
       <c r="F42" t="n">
         <v>0.311679674</v>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1296,6 +1506,11 @@
       <c r="F43" t="n">
         <v>0.328983913</v>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1316,6 +1531,11 @@
       <c r="F44" t="n">
         <v>0</v>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1336,6 +1556,11 @@
       <c r="F45" t="n">
         <v>0.047106137</v>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1356,6 +1581,11 @@
       <c r="F46" t="n">
         <v>0.11113812</v>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1376,6 +1606,11 @@
       <c r="F47" t="n">
         <v>0.157101032</v>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1396,6 +1631,11 @@
       <c r="F48" t="n">
         <v>0.17723433</v>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1416,6 +1656,11 @@
       <c r="F49" t="n">
         <v>0.203199262</v>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1436,6 +1681,11 @@
       <c r="F50" t="n">
         <v>0.226319718</v>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1456,6 +1706,11 @@
       <c r="F51" t="n">
         <v>0.236380218</v>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1476,6 +1731,11 @@
       <c r="F52" t="n">
         <v>0.249815332</v>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1496,6 +1756,11 @@
       <c r="F53" t="n">
         <v>0.256419902</v>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1516,6 +1781,11 @@
       <c r="F54" t="n">
         <v>0.267696194</v>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1536,6 +1806,11 @@
       <c r="F55" t="n">
         <v>0.274482585</v>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1556,6 +1831,11 @@
       <c r="F56" t="n">
         <v>0.284523431</v>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1576,6 +1856,11 @@
       <c r="F57" t="n">
         <v>0.293058926</v>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1596,6 +1881,11 @@
       <c r="F58" t="n">
         <v>0</v>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1616,6 +1906,11 @@
       <c r="F59" t="n">
         <v>0.056957217</v>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1636,6 +1931,11 @@
       <c r="F60" t="n">
         <v>0.12191595</v>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1656,6 +1956,11 @@
       <c r="F61" t="n">
         <v>0.160936952</v>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1676,6 +1981,11 @@
       <c r="F62" t="n">
         <v>0.182634575</v>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1696,6 +2006,11 @@
       <c r="F63" t="n">
         <v>0.201941282</v>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1716,6 +2031,11 @@
       <c r="F64" t="n">
         <v>0.21599597</v>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1736,6 +2056,11 @@
       <c r="F65" t="n">
         <v>0.226452432</v>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1756,6 +2081,11 @@
       <c r="F66" t="n">
         <v>0.236165263</v>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1776,6 +2106,11 @@
       <c r="F67" t="n">
         <v>0.241661312</v>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1796,6 +2131,11 @@
       <c r="F68" t="n">
         <v>0.25280654</v>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1816,6 +2156,11 @@
       <c r="F69" t="n">
         <v>0.256525252</v>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1836,6 +2181,11 @@
       <c r="F70" t="n">
         <v>0.263765982</v>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1856,6 +2206,11 @@
       <c r="F71" t="n">
         <v>0.269507547</v>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1876,6 +2231,11 @@
       <c r="F72" t="n">
         <v>0</v>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1896,6 +2256,11 @@
       <c r="F73" t="n">
         <v>0.019744472</v>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1916,6 +2281,11 @@
       <c r="F74" t="n">
         <v>0.068837342</v>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1936,6 +2306,11 @@
       <c r="F75" t="n">
         <v>0.09732962000000001</v>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1956,6 +2331,11 @@
       <c r="F76" t="n">
         <v>0.116186997</v>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1976,6 +2356,11 @@
       <c r="F77" t="n">
         <v>0.129812368</v>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1996,6 +2381,11 @@
       <c r="F78" t="n">
         <v>0.140117701</v>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2016,6 +2406,11 @@
       <c r="F79" t="n">
         <v>0.149682126</v>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2036,6 +2431,11 @@
       <c r="F80" t="n">
         <v>0.155513347</v>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2056,6 +2456,11 @@
       <c r="F81" t="n">
         <v>0.162426774</v>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2076,6 +2481,11 @@
       <c r="F82" t="n">
         <v>0.167631151</v>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2096,6 +2506,11 @@
       <c r="F83" t="n">
         <v>0.17251227</v>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2116,6 +2531,11 @@
       <c r="F84" t="n">
         <v>0.180976271</v>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2135,6 +2555,11 @@
       </c>
       <c r="F85" t="n">
         <v>0.185595806</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2255,102 +2680,102 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" t="n">
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.486666667</v>
+        <v>0.023333333</v>
       </c>
       <c r="E2" t="n">
-        <v>1.089375</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.019744472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.67</v>
+        <v>0.486666667</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2621875</v>
+        <v>1.089375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.068837342</v>
+        <v>0.019744472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>1.349375</v>
+        <v>1.2621875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09732962000000001</v>
+        <v>0.068837342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" t="n">
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>0.813333333</v>
+        <v>0.76</v>
       </c>
       <c r="E5" t="n">
-        <v>1.40609375</v>
+        <v>1.349375</v>
       </c>
       <c r="F5" t="n">
-        <v>0.116186997</v>
+        <v>0.09732962000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" t="n">
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D6" t="n">
-        <v>0.846666667</v>
+        <v>0.813333333</v>
       </c>
       <c r="E6" t="n">
-        <v>1.44921875</v>
+        <v>1.40609375</v>
       </c>
       <c r="F6" t="n">
-        <v>0.129812368</v>
+        <v>0.116186997</v>
       </c>
     </row>
     <row r="7">
@@ -2375,22 +2800,22 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" t="n">
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D8" t="n">
-        <v>0.903333333</v>
+        <v>0.916666667</v>
       </c>
       <c r="E8" t="n">
-        <v>1.50375</v>
+        <v>1.52203125</v>
       </c>
       <c r="F8" t="n">
-        <v>0.149682126</v>
+        <v>0.155513347</v>
       </c>
     </row>
     <row r="9">
@@ -2455,22 +2880,22 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" t="n">
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D12" t="n">
-        <v>0.993333333</v>
+        <v>0.9866666670000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.60703125</v>
+        <v>1.589375</v>
       </c>
       <c r="F12" t="n">
-        <v>0.185595806</v>
+        <v>0.180976271</v>
       </c>
     </row>
     <row r="13">
@@ -2495,222 +2920,222 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" t="n">
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>0.413333333</v>
+        <v>0.606666667</v>
       </c>
       <c r="E14" t="n">
-        <v>1.385364496</v>
+        <v>1.682526433</v>
       </c>
       <c r="F14" t="n">
-        <v>0.056957217</v>
+        <v>0.12191595</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B15" t="n">
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>0.706666667</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.850862549</v>
+        <v>2.013077351</v>
       </c>
       <c r="F15" t="n">
-        <v>0.160936952</v>
+        <v>0.201941282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B16" t="n">
         <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D16" t="n">
-        <v>0.766666667</v>
+        <v>0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>1.926265999</v>
+        <v>2.053144129</v>
       </c>
       <c r="F16" t="n">
-        <v>0.182634575</v>
+        <v>0.21599597</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B17" t="n">
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.873333333</v>
       </c>
       <c r="E17" t="n">
-        <v>2.013077351</v>
+        <v>2.098219254</v>
       </c>
       <c r="F17" t="n">
-        <v>0.201941282</v>
+        <v>0.226452432</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B18" t="n">
         <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D18" t="n">
-        <v>0.85</v>
+        <v>0.903333333</v>
       </c>
       <c r="E18" t="n">
-        <v>2.053144129</v>
+        <v>2.117417919</v>
       </c>
       <c r="F18" t="n">
-        <v>0.21599597</v>
+        <v>0.236165263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D19" t="n">
-        <v>0.903333333</v>
+        <v>0.916666667</v>
       </c>
       <c r="E19" t="n">
-        <v>2.117417919</v>
+        <v>2.137451308</v>
       </c>
       <c r="F19" t="n">
-        <v>0.236165263</v>
+        <v>0.241661312</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B20" t="n">
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D20" t="n">
-        <v>0.916666667</v>
+        <v>0.946666667</v>
       </c>
       <c r="E20" t="n">
-        <v>2.137451308</v>
+        <v>2.169449082</v>
       </c>
       <c r="F20" t="n">
-        <v>0.241661312</v>
+        <v>0.25280654</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B21" t="n">
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="D21" t="n">
-        <v>0.946666667</v>
+        <v>0.95</v>
       </c>
       <c r="E21" t="n">
-        <v>2.169449082</v>
+        <v>2.198107958</v>
       </c>
       <c r="F21" t="n">
-        <v>0.25280654</v>
+        <v>0.256525252</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" t="n">
         <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="D22" t="n">
-        <v>0.95</v>
+        <v>0.973333333</v>
       </c>
       <c r="E22" t="n">
-        <v>2.198107958</v>
+        <v>2.207568169</v>
       </c>
       <c r="F22" t="n">
-        <v>0.256525252</v>
+        <v>0.263765982</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" t="n">
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D23" t="n">
-        <v>0.973333333</v>
+        <v>0.9866666670000001</v>
       </c>
       <c r="E23" t="n">
-        <v>2.207568169</v>
+        <v>2.228992766</v>
       </c>
       <c r="F23" t="n">
-        <v>0.263765982</v>
+        <v>0.269507547</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" t="n">
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.306666667</v>
+        <v>0.043333333</v>
       </c>
       <c r="E24" t="n">
-        <v>1.461111111</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.047106137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2795,42 +3220,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29" t="n">
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D29" t="n">
-        <v>0.796666667</v>
+        <v>0.826666667</v>
       </c>
       <c r="E29" t="n">
-        <v>2.400854701</v>
+        <v>2.423076923</v>
       </c>
       <c r="F29" t="n">
-        <v>0.226319718</v>
+        <v>0.236380218</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" t="n">
         <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D30" t="n">
-        <v>0.826666667</v>
+        <v>0.86</v>
       </c>
       <c r="E30" t="n">
-        <v>2.423076923</v>
+        <v>2.479059829</v>
       </c>
       <c r="F30" t="n">
-        <v>0.236380218</v>
+        <v>0.249815332</v>
       </c>
     </row>
     <row r="31">
@@ -2915,22 +3340,22 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" t="n">
         <v>12</v>
       </c>
       <c r="C35" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.24</v>
+        <v>0.046666667</v>
       </c>
       <c r="E35" t="n">
-        <v>1.710181137</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.049264635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3035,22 +3460,22 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" t="n">
         <v>12</v>
       </c>
       <c r="C41" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D41" t="n">
-        <v>0.826666667</v>
+        <v>0.786666667</v>
       </c>
       <c r="E41" t="n">
-        <v>3.090568395</v>
+        <v>3.026858214</v>
       </c>
       <c r="F41" t="n">
-        <v>0.276412389</v>
+        <v>0.260389238</v>
       </c>
     </row>
     <row r="42">
@@ -3135,182 +3560,182 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B46" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D46" t="n">
-        <v>0.043333333</v>
+        <v>0.956666667</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>3.286071205</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.328983913</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" t="n">
         <v>14</v>
       </c>
       <c r="C47" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.156666667</v>
+        <v>0.043333333</v>
       </c>
       <c r="E47" t="n">
-        <v>1.730934019</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.032958996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B48" t="n">
         <v>14</v>
       </c>
       <c r="C48" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D48" t="n">
-        <v>0.39</v>
+        <v>0.156666667</v>
       </c>
       <c r="E48" t="n">
-        <v>2.292202228</v>
+        <v>1.730934019</v>
       </c>
       <c r="F48" t="n">
-        <v>0.109532278</v>
+        <v>0.032958996</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B49" t="n">
         <v>14</v>
       </c>
       <c r="C49" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D49" t="n">
-        <v>0.576666667</v>
+        <v>0.39</v>
       </c>
       <c r="E49" t="n">
-        <v>3.068551842</v>
+        <v>2.292202228</v>
       </c>
       <c r="F49" t="n">
-        <v>0.193668002</v>
+        <v>0.109532278</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B50" t="n">
         <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D50" t="n">
-        <v>0.643333333</v>
+        <v>0.496666667</v>
       </c>
       <c r="E50" t="n">
-        <v>3.179091688</v>
+        <v>2.65638389</v>
       </c>
       <c r="F50" t="n">
-        <v>0.219689143</v>
+        <v>0.154289085</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B51" t="n">
         <v>14</v>
       </c>
       <c r="C51" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>0.71</v>
+        <v>0.576666667</v>
       </c>
       <c r="E51" t="n">
-        <v>3.40874036</v>
+        <v>3.068551842</v>
       </c>
       <c r="F51" t="n">
-        <v>0.249950795</v>
+        <v>0.193668002</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B52" t="n">
         <v>14</v>
       </c>
       <c r="C52" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D52" t="n">
-        <v>0.753333333</v>
+        <v>0.71</v>
       </c>
       <c r="E52" t="n">
-        <v>3.485861183</v>
+        <v>3.40874036</v>
       </c>
       <c r="F52" t="n">
-        <v>0.267641886</v>
+        <v>0.249950795</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B53" t="n">
         <v>14</v>
       </c>
       <c r="C53" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="D53" t="n">
-        <v>0.83</v>
+        <v>0.753333333</v>
       </c>
       <c r="E53" t="n">
-        <v>3.600685518</v>
+        <v>3.485861183</v>
       </c>
       <c r="F53" t="n">
-        <v>0.298662612</v>
+        <v>0.267641886</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B54" t="n">
         <v>14</v>
       </c>
       <c r="C54" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="D54" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="E54" t="n">
-        <v>3.618680377</v>
+        <v>3.525278492</v>
       </c>
       <c r="F54" t="n">
-        <v>0.306444136</v>
+        <v>0.281931145</v>
       </c>
     </row>
     <row r="55">
@@ -3335,262 +3760,262 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B56" t="n">
         <v>14</v>
       </c>
       <c r="C56" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D56" t="n">
-        <v>0.946666667</v>
+        <v>0.903333333</v>
       </c>
       <c r="E56" t="n">
-        <v>3.829477292</v>
+        <v>3.77377892</v>
       </c>
       <c r="F56" t="n">
-        <v>0.348468826</v>
+        <v>0.330783285</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B57" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D57" t="n">
-        <v>0.026666667</v>
+        <v>0.946666667</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3.829477292</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>0.348468826</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B58" t="n">
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.123333333</v>
+        <v>0.026666667</v>
       </c>
       <c r="E58" t="n">
-        <v>1.606026786</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0.023115971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B59" t="n">
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D59" t="n">
-        <v>0.316666667</v>
+        <v>0.123333333</v>
       </c>
       <c r="E59" t="n">
-        <v>2.622767857</v>
+        <v>1.606026786</v>
       </c>
       <c r="F59" t="n">
-        <v>0.09732608700000001</v>
+        <v>0.023115971</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B60" t="n">
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D60" t="n">
-        <v>0.526666667</v>
+        <v>0.45</v>
       </c>
       <c r="E60" t="n">
-        <v>3.291294643</v>
+        <v>3.094866071</v>
       </c>
       <c r="F60" t="n">
-        <v>0.182132285</v>
+        <v>0.151308161</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B61" t="n">
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>0.603333333</v>
+        <v>0.526666667</v>
       </c>
       <c r="E61" t="n">
-        <v>3.522321429</v>
+        <v>3.291294643</v>
       </c>
       <c r="F61" t="n">
-        <v>0.214618498</v>
+        <v>0.182132285</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B62" t="n">
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D62" t="n">
-        <v>0.64</v>
+        <v>0.603333333</v>
       </c>
       <c r="E62" t="n">
-        <v>3.853794643</v>
+        <v>3.522321429</v>
       </c>
       <c r="F62" t="n">
-        <v>0.235425874</v>
+        <v>0.214618498</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B63" t="n">
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D63" t="n">
-        <v>0.753333333</v>
+        <v>0.64</v>
       </c>
       <c r="E63" t="n">
-        <v>4.049107143</v>
+        <v>3.853794643</v>
       </c>
       <c r="F63" t="n">
-        <v>0.281800324</v>
+        <v>0.235425874</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B64" t="n">
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="D64" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>4.332589286</v>
+        <v>3.943080357</v>
       </c>
       <c r="F64" t="n">
-        <v>0.305679394</v>
+        <v>0.255832691</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B65" t="n">
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="D65" t="n">
-        <v>0.833333333</v>
+        <v>0.753333333</v>
       </c>
       <c r="E65" t="n">
-        <v>4.2421875</v>
+        <v>4.049107143</v>
       </c>
       <c r="F65" t="n">
-        <v>0.316379708</v>
+        <v>0.281800324</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B66" t="n">
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="D66" t="n">
-        <v>0.863333333</v>
+        <v>0.8</v>
       </c>
       <c r="E66" t="n">
-        <v>4.3046875</v>
+        <v>4.332589286</v>
       </c>
       <c r="F66" t="n">
-        <v>0.329237345</v>
+        <v>0.305679394</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B67" t="n">
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="D67" t="n">
-        <v>0.916666667</v>
+        <v>0.833333333</v>
       </c>
       <c r="E67" t="n">
-        <v>4.464285714</v>
+        <v>4.2421875</v>
       </c>
       <c r="F67" t="n">
-        <v>0.35335845</v>
+        <v>0.316379708</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B68" t="n">
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.916666667</v>
       </c>
       <c r="E68" t="n">
-        <v>4.681919643</v>
+        <v>4.464285714</v>
       </c>
       <c r="F68" t="n">
-        <v>0.367215621</v>
+        <v>0.35335845</v>
       </c>
     </row>
   </sheetData>
@@ -3641,162 +4066,162 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B2" t="n">
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023333333</v>
+        <v>0.846666667</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>1.44921875</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.129812368</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D3" t="n">
-        <v>0.916666667</v>
+        <v>0.903333333</v>
       </c>
       <c r="E3" t="n">
-        <v>1.52203125</v>
+        <v>1.50375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.155513347</v>
+        <v>0.149682126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9866666670000001</v>
+        <v>0.993333333</v>
       </c>
       <c r="E4" t="n">
-        <v>1.589375</v>
+        <v>1.60703125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.180976271</v>
+        <v>0.185595806</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" t="n">
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>0.606666667</v>
+        <v>0.413333333</v>
       </c>
       <c r="E5" t="n">
-        <v>1.682526433</v>
+        <v>1.385364496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12191595</v>
+        <v>0.056957217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" t="n">
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>0.873333333</v>
+        <v>0.706666667</v>
       </c>
       <c r="E6" t="n">
-        <v>2.098219254</v>
+        <v>1.850862549</v>
       </c>
       <c r="F6" t="n">
-        <v>0.226452432</v>
+        <v>0.160936952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B7" t="n">
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9866666670000001</v>
+        <v>0.766666667</v>
       </c>
       <c r="E7" t="n">
-        <v>2.228992766</v>
+        <v>1.926265999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.269507547</v>
+        <v>0.182634575</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>0.043333333</v>
+        <v>0.306666667</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>1.461111111</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.047106137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" t="n">
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D9" t="n">
-        <v>0.86</v>
+        <v>0.796666667</v>
       </c>
       <c r="E9" t="n">
-        <v>2.479059829</v>
+        <v>2.400854701</v>
       </c>
       <c r="F9" t="n">
-        <v>0.249815332</v>
+        <v>0.226319718</v>
       </c>
     </row>
     <row r="10">
@@ -3821,162 +4246,162 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="n">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>0.046666667</v>
+        <v>0.24</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>1.710181137</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.049264635</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="n">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>0.786666667</v>
+        <v>0.826666667</v>
       </c>
       <c r="E12" t="n">
-        <v>3.026858214</v>
+        <v>3.090568395</v>
       </c>
       <c r="F12" t="n">
-        <v>0.260389238</v>
+        <v>0.276412389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>0.956666667</v>
+        <v>0.643333333</v>
       </c>
       <c r="E13" t="n">
-        <v>3.286071205</v>
+        <v>3.179091688</v>
       </c>
       <c r="F13" t="n">
-        <v>0.328983913</v>
+        <v>0.219689143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>0.496666667</v>
+        <v>0.83</v>
       </c>
       <c r="E14" t="n">
-        <v>2.65638389</v>
+        <v>3.600685518</v>
       </c>
       <c r="F14" t="n">
-        <v>0.154289085</v>
+        <v>0.298662612</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="D15" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="E15" t="n">
-        <v>3.525278492</v>
+        <v>3.618680377</v>
       </c>
       <c r="F15" t="n">
-        <v>0.281931145</v>
+        <v>0.306444136</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>0.903333333</v>
+        <v>0.316666667</v>
       </c>
       <c r="E16" t="n">
-        <v>3.77377892</v>
+        <v>2.622767857</v>
       </c>
       <c r="F16" t="n">
-        <v>0.330783285</v>
+        <v>0.09732608700000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="D17" t="n">
-        <v>0.45</v>
+        <v>0.863333333</v>
       </c>
       <c r="E17" t="n">
-        <v>3.094866071</v>
+        <v>4.3046875</v>
       </c>
       <c r="F17" t="n">
-        <v>0.151308161</v>
+        <v>0.329237345</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>3.943080357</v>
+        <v>4.681919643</v>
       </c>
       <c r="F18" t="n">
-        <v>0.255832691</v>
+        <v>0.367215621</v>
       </c>
     </row>
   </sheetData>
@@ -4032,47 +4457,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B2" t="n">
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023333333</v>
+        <v>0.846666667</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>1.44921875</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.129812368</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D3" t="n">
-        <v>0.916666667</v>
+        <v>0.903333333</v>
       </c>
       <c r="E3" t="n">
-        <v>1.52203125</v>
+        <v>1.50375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.155513347</v>
+        <v>0.149682126</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4082,22 +4507,22 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9866666670000001</v>
+        <v>0.993333333</v>
       </c>
       <c r="E4" t="n">
-        <v>1.589375</v>
+        <v>1.60703125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.180976271</v>
+        <v>0.185595806</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -4107,22 +4532,22 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" t="n">
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>0.606666667</v>
+        <v>0.413333333</v>
       </c>
       <c r="E5" t="n">
-        <v>1.682526433</v>
+        <v>1.385364496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12191595</v>
+        <v>0.056957217</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4132,72 +4557,72 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" t="n">
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>0.873333333</v>
+        <v>0.706666667</v>
       </c>
       <c r="E6" t="n">
-        <v>2.098219254</v>
+        <v>1.850862549</v>
       </c>
       <c r="F6" t="n">
-        <v>0.226452432</v>
+        <v>0.160936952</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B7" t="n">
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9866666670000001</v>
+        <v>0.766666667</v>
       </c>
       <c r="E7" t="n">
-        <v>2.228992766</v>
+        <v>1.926265999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.269507547</v>
+        <v>0.182634575</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>0.043333333</v>
+        <v>0.306666667</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>1.461111111</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.047106137</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4207,22 +4632,22 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" t="n">
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D9" t="n">
-        <v>0.86</v>
+        <v>0.796666667</v>
       </c>
       <c r="E9" t="n">
-        <v>2.479059829</v>
+        <v>2.400854701</v>
       </c>
       <c r="F9" t="n">
-        <v>0.249815332</v>
+        <v>0.226319718</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4257,22 +4682,22 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="n">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>0.046666667</v>
+        <v>0.24</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>1.710181137</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.049264635</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4282,22 +4707,22 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="n">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>0.786666667</v>
+        <v>0.826666667</v>
       </c>
       <c r="E12" t="n">
-        <v>3.026858214</v>
+        <v>3.090568395</v>
       </c>
       <c r="F12" t="n">
-        <v>0.260389238</v>
+        <v>0.276412389</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -4307,151 +4732,151 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>0.956666667</v>
+        <v>0.643333333</v>
       </c>
       <c r="E13" t="n">
-        <v>3.286071205</v>
+        <v>3.179091688</v>
       </c>
       <c r="F13" t="n">
-        <v>0.328983913</v>
+        <v>0.219689143</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>0.496666667</v>
+        <v>0.83</v>
       </c>
       <c r="E14" t="n">
-        <v>2.65638389</v>
+        <v>3.600685518</v>
       </c>
       <c r="F14" t="n">
-        <v>0.154289085</v>
+        <v>0.298662612</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="D15" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="E15" t="n">
-        <v>3.525278492</v>
+        <v>3.618680377</v>
       </c>
       <c r="F15" t="n">
-        <v>0.281931145</v>
+        <v>0.306444136</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>0.903333333</v>
+        <v>0.316666667</v>
       </c>
       <c r="E16" t="n">
-        <v>3.77377892</v>
+        <v>2.622767857</v>
       </c>
       <c r="F16" t="n">
-        <v>0.330783285</v>
+        <v>0.09732608700000001</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="D17" t="n">
-        <v>0.45</v>
+        <v>0.863333333</v>
       </c>
       <c r="E17" t="n">
-        <v>3.094866071</v>
+        <v>4.3046875</v>
       </c>
       <c r="F17" t="n">
-        <v>0.151308161</v>
+        <v>0.329237345</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>3.943080357</v>
+        <v>4.681919643</v>
       </c>
       <c r="F18" t="n">
-        <v>0.255832691</v>
+        <v>0.367215621</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4529,7 +4954,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fixed experimental (d, RPM) coordinates</t>
+          <t>Stratified by RPM region; diameter counts constrained to 2-3 per diameter</t>
         </is>
       </c>
     </row>
@@ -4539,52 +4964,50 @@
           <t>Random seed</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not used; locked Point_ID list retained</t>
-        </is>
+      <c r="B7" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Test Point_IDs</t>
+          <t>RPM region allocation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>71, 79, 83, 59, 64, 70, 43, 51, 53, 29, 36, 42, 18, 23, 27, 4, 8</t>
+          <t>{'Low': 6, 'Medium': 6, 'High': 5}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Target variables</t>
+          <t>Test Point_IDs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hc_hi, td_to, Vch</t>
+          <t>3, 12, 14, 20, 24, 25, 30, 37, 44, 49, 53, 58, 60, 61, 76, 78, 84</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Synthetic interpolation used</t>
+          <t>Target variables</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>hc_hi, td_to, Vch</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Extrapolation used</t>
+          <t>Synthetic interpolation used</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4596,17 +5019,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Test-coordinate leakage</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
+          <t>Extrapolation used</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Point_ID leakage</t>
+          <t>Test-coordinate leakage</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4616,10 +5041,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Point_ID leakage</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
@@ -4705,16 +5140,16 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>240</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
         <v>260</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>240</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -4740,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H3" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -4769,13 +5204,13 @@
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>260</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
         <v>200</v>
@@ -4792,25 +5227,25 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>260</v>
+      </c>
+      <c r="G5" t="n">
         <v>20</v>
       </c>
-      <c r="F5" t="n">
-        <v>240</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -4839,10 +5274,10 @@
         <v>260</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -4856,10 +5291,10 @@
         <v>16</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
@@ -4868,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>240</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" t="n">
         <v>260</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="n">
-        <v>140</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -5041,16 +5476,16 @@
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>0.026666667</v>
+        <v>0.023333333</v>
       </c>
       <c r="E2" t="n">
+        <v>0.9866666670000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.993333333</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.023333333</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.9866666670000001</v>
       </c>
       <c r="H2" t="n">
         <v>0.023333333</v>
@@ -5075,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
+        <v>4.464285714</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.385364496</v>
+      </c>
+      <c r="G3" t="n">
         <v>4.681919643</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.943080357</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -5106,13 +5541,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>0.35335845</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.047106137</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.367215621</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.330783285</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -5184,7 +5619,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -5199,10 +5634,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.026666667</v>
+        <v>0.023333333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.043333333</v>
+        <v>0.046666667</v>
       </c>
     </row>
     <row r="3">
@@ -5212,26 +5647,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.023333333</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.046666667</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
